--- a/mode_docx_nc/pmi_ka/ka_modes/КА_39.xlsx
+++ b/mode_docx_nc/pmi_ka/ka_modes/КА_39.xlsx
@@ -437,35 +437,6 @@
   </sheetPr>
   <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -565,32 +536,32 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rbrf1_tpbrf</t>
+          <t>SGF1_genrbrf1_tpbrf</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_rbrf1_tpbrf</t>
+          <t>SGF2_genrbrf1_tpbrf</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_rbrf1_tpbrf</t>
+          <t>SGF3_genrbrf1_tpbrf</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_rbrf1_tpbrf</t>
+          <t>SGF4_genrbrf1_tpbrf</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_rbrf1_tpbrf</t>
+          <t>SGF5_genrbrf1_tpbrf</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_rbrf1_tpbrf</t>
+          <t>SGF6_genrbrf1_tpbrf</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -605,7 +576,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
@@ -629,40 +600,40 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" s="2" t="n">
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
@@ -680,7 +651,7 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
@@ -700,23 +671,6 @@
   </sheetPr>
   <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -781,12 +735,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>T1_rbrf1_tpbrf</t>
+          <t>T1_genrbrf1_tpbrf</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Iset_rbrf1_tpbrf</t>
+          <t>Iset_genrbrf1_tpbrf</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -796,49 +750,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.5</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" t="n">
         <v>0.5</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="n">
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.2</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" t="n">
         <v>1</v>
       </c>
     </row>
